--- a/XlsxSharp.Tests/Resource/Other/Unicode/let_it_go_in_emoji-outputfile.xlsx
+++ b/XlsxSharp.Tests/Resource/Other/Unicode/let_it_go_in_emoji-outputfile.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-  </x:sheets>
-  <x:definedNames/>
-  <x:calcPr calcId="125725"/>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView firstSheet="0" activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet r:id="rId1" name="Sheet1" sheetId="1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="125725"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>This emoji version of Let It Go from Frozen:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The ❄️ 🌟 🔦 ⚪ on the mountain 🌙 🌠. 🙅🏻 a👣 to 🐝  👀. A 🏰 of 😢, and it 👀  like☝️️ the 👑. The 💨 is 🐺 like this 🌀 ❄️ ☔️ 🏠. 🙅🏻 keep it in, ☁️ 💡 ☝️️ tried. 🙅🏻 let 👬👫 in,🙅🏻 let 👬👫 👀. 🐝 the 👍  👧  👇 always have to 🐝. 🙅🏻, don't 👐, 🚫 let 👬👫💡. Well now 👬👫 💡. 👐 it 🚗,, 👐 it 🚗,,🙅🏻 ✊ it back anymore. 👐 it 🚗,, 👐 it 🚗,  turn ✈️ and 🔨 the 🚪. ☝️️ 🚫 care, what 👬👫  going to 👄, let the ☔️ ⚡ ❄️  😡 on, the ❄️ ⛄️ 🙅🏻 bothered ☝️️ anyway. It's 😜😂  how some ✈️ 🚆 makes everything 😳  🐜. And the 😱  that once 👮  me, 🙅🏻 get to☝️️ at all. It's 🕓  to 👀  what☝️️ can do. To 📝 the 📊 and 🔨 through. 🚫 👍 , 🚫  👎, 🚫  👮 for ☝️️. ☝️️ 🏃. 👐 it 🚗,, 👐 it 🚗., ☝️️ am ☝️ with the 🌀  and 🌌. 👐 it 🚗,, 👐 it 🚗..👇 🙅🏻 👀  ☝️️  😭 .  👉 ☝️️ 🚶, and 👉 ☝️️ stay. Let the⚡ ❄️ 😡 on. ☝️️ 💪 ❄️ through the 🌀 into the 🌎.☝️️ 👤 is 🌀 in ❄️ ⛄️ fractals all 🔁. And 1️⃣💡 💎 like an ❄️ 📢.  ☝️️ 🙅🏻 🏃 back, the past is in the past. 👐 it 🚗,,👐 it 🚗,. And ☝️️ 🚀 like the 💔 of 🌌. 👐 it 🚗,, 👐 it 🚗.. That 💁 is 🚫. Here ☝️️ 🚶, in the 🔦 of ☀️. Let the ⚡ ❄️  😡  on, the ❄️ ⛄️ 🙅🏻 bothered ☝️️ anyway.</x:t>
-  </x:si>
-</x:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <si>
+    <t>This emoji version of Let It Go from Frozen:</t>
+  </si>
+  <si>
+    <t>The ❄️ 🌟 🔦 ⚪ on the mountain 🌙 🌠. 🙅🏻 a👣 to 🐝  👀. A 🏰 of 😢, and it 👀  like☝️️ the 👑. The 💨 is 🐺 like this 🌀 ❄️ ☔️ 🏠. 🙅🏻 keep it in, ☁️ 💡 ☝️️ tried. 🙅🏻 let 👬👫 in,🙅🏻 let 👬👫 👀. 🐝 the 👍  👧  👇 always have to 🐝. 🙅🏻, don't 👐, 🚫 let 👬👫💡. Well now 👬👫 💡. 👐 it 🚗,, 👐 it 🚗,,🙅🏻 ✊ it back anymore. 👐 it 🚗,, 👐 it 🚗,  turn ✈️ and 🔨 the 🚪. ☝️️ 🚫 care, what 👬👫  going to 👄, let the ☔️ ⚡ ❄️  😡 on, the ❄️ ⛄️ 🙅🏻 bothered ☝️️ anyway. It's 😜😂  how some ✈️ 🚆 makes everything 😳  🐜. And the 😱  that once 👮  me, 🙅🏻 get to☝️️ at all. It's 🕓  to 👀  what☝️️ can do. To 📝 the 📊 and 🔨 through. 🚫 👍 , 🚫  👎, 🚫  👮 for ☝️️. ☝️️ 🏃. 👐 it 🚗,, 👐 it 🚗., ☝️️ am ☝️ with the 🌀  and 🌌. 👐 it 🚗,, 👐 it 🚗..👇 🙅🏻 👀  ☝️️  😭 .  👉 ☝️️ 🚶, and 👉 ☝️️ stay. Let the⚡ ❄️ 😡 on. ☝️️ 💪 ❄️ through the 🌀 into the 🌎.☝️️ 👤 is 🌀 in ❄️ ⛄️ fractals all 🔁. And 1️⃣💡 💎 like an ❄️ 📢.  ☝️️ 🙅🏻 🏃 back, the past is in the past. 👐 it 🚗,,👐 it 🚗,. And ☝️️ 🚀 like the 💔 of 🌌. 👐 it 🚗,, 👐 it 🚗.. That 💁 is 🚫. Here ☝️️ 🚶, in the 🔦 of ☀️. Let the ⚡ ❄️  😡  on, the ❄️ ⛄️ 🙅🏻 bothered ☝️️ anyway.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -357,28 +357,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:A2"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1" spans="1:1">
-      <x:c r="A1" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:1">
-      <x:c r="A2" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>